--- a/data/usa/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/usa/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,226 +448,246 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AszX60rp</t>
+          <t>hQiNHHd2</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="C2" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jix3jCxF</t>
+          <t>C6QBlj7R</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>h6Py6Kcj</t>
+          <t>dbI3Q902</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WdOu5vDd</t>
+          <t>zkH7PTF8</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>KCHNTNkc</t>
+          <t>UPVAOmVE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="C6" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>b3GRSs53</t>
+          <t>8GUEN7pL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="C7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D7" t="n">
         <v>3.9</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>tS5WR1K9</t>
+          <t>juKJMRaR</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="C8" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>h29zRLZF</t>
+          <t>Usy7kWiL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="C9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D9" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>QF7rPa4S</t>
+          <t>lSHwpAFr</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="C10" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="D10" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>nP8vQukM</t>
+          <t>MNAkH5Nl</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="C11" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="D11" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>69kBKJCq</t>
+          <t>S0BoIo8r</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="C12" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="D12" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>vNmJIcsd</t>
+          <t>0E9gGPxe</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="C13" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>3.2</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>MHXbihN8</t>
+          <t>Ik4bFqh1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="C14" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>p0lFJwSk</t>
+          <t>dt32E377</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="C15" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2</v>
-      </c>
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>vqenBDBt</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>SWX9C8ZI</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/usa/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/usa/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,246 +448,98 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hQiNHHd2</t>
+          <t>hIoLKAg0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="D2" t="n">
-        <v>2.88</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>C6QBlj7R</t>
+          <t>KEflYcbt</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="C3" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dbI3Q902</t>
+          <t>EyfhXHDn</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="C4" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>zkH7PTF8</t>
+          <t>SvbdWyTh</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>UPVAOmVE</t>
+          <t>AoWGqXpJ</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="C6" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="D6" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>8GUEN7pL</t>
+          <t>trWntSE7</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="C7" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="D7" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>juKJMRaR</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Usy7kWiL</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>lSHwpAFr</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>MNAkH5Nl</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>S0BoIo8r</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>0E9gGPxe</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="C13" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" t="n">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Ik4bFqh1</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="C14" t="n">
-        <v>4</v>
-      </c>
-      <c r="D14" t="n">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>dt32E377</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D15" t="n">
         <v>3.8</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>vqenBDBt</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>SWX9C8ZI</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/usa/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/usa/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,7 +474,7 @@
         <v>3.4</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="4">
@@ -503,7 +503,7 @@
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D5" t="n">
         <v>3.6</v>
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="C6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="7">
@@ -532,13 +532,221 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="C7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>A3m1Vera</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8lOY3V6E</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ITj9TZCB</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>lfn5UFc5</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>dKkDSgSH</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>vquIRDsO</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>jDDw3kMK</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D14" t="n">
         <v>3.5</v>
       </c>
-      <c r="D7" t="n">
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>xUcLQXdU</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>EkZQoHSu</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C16" t="n">
         <v>3.8</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>htYUpyrn</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AHSZqech</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>l8RwqFCb</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>foKU4Bi8</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/usa/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/usa/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,306 +448,356 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hIoLKAg0</t>
+          <t>A3m1Vera</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="C2" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>KEflYcbt</t>
+          <t>8lOY3V6E</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="C3" t="n">
         <v>3.4</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EyfhXHDn</t>
+          <t>ITj9TZCB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="C4" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SvbdWyTh</t>
+          <t>lfn5UFc5</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="C5" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>AoWGqXpJ</t>
+          <t>dKkDSgSH</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="C6" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="D6" t="n">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>trWntSE7</t>
+          <t>vquIRDsO</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.05</v>
+        <v>1.47</v>
       </c>
       <c r="C7" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="D7" t="n">
-        <v>3.6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>A3m1Vera</t>
+          <t>jDDw3kMK</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="C8" t="n">
         <v>3.75</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8lOY3V6E</t>
+          <t>xUcLQXdU</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="C9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="D9" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ITj9TZCB</t>
+          <t>EkZQoHSu</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="C10" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="D10" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>lfn5UFc5</t>
+          <t>htYUpyrn</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="C11" t="n">
         <v>3.6</v>
       </c>
       <c r="D11" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>dKkDSgSH</t>
+          <t>AHSZqech</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="C12" t="n">
         <v>3.8</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>vquIRDsO</t>
+          <t>l8RwqFCb</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.66</v>
+        <v>2.45</v>
       </c>
       <c r="C13" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="D13" t="n">
-        <v>4.75</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>jDDw3kMK</t>
+          <t>foKU4Bi8</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="C14" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>xUcLQXdU</t>
+          <t>rVQsrZR4</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="C15" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>EkZQoHSu</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3.2</v>
-      </c>
+          <t>dYUosgsB</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>htYUpyrn</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3.5</v>
-      </c>
+          <t>U3Cs29yR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>AHSZqech</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2.8</v>
-      </c>
+          <t>vcKjtDdH</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>l8RwqFCb</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2.5</v>
-      </c>
+          <t>Me49cTqr</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>foKU4Bi8</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="C20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="D20" t="n">
-        <v>6.5</v>
-      </c>
+          <t>ImJfuXBN</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>0n3Ddmal</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>SM4QZAZp</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>URr9bfCo</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>QDIbviRT</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>rVnDcERi</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xhnHdYtb</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>GroLehd4</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YJuQfCBA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/usa/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/usa/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,10 +455,10 @@
         <v>1.7</v>
       </c>
       <c r="C2" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="3">
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="C3" t="n">
         <v>3.4</v>
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="C4" t="n">
         <v>3.5</v>
       </c>
       <c r="D4" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="5">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="C5" t="n">
         <v>3.8</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="C6" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="D6" t="n">
-        <v>5.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="C7" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="D7" t="n">
         <v>6.1</v>
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="C8" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="D8" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="9">
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="C9" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D9" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="10">
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="C10" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="11">
@@ -596,13 +596,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
         <v>3.6</v>
       </c>
       <c r="D11" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="12">
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="C12" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="13">
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="C13" t="n">
         <v>3.7</v>
       </c>
       <c r="D13" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="14">
@@ -647,7 +647,7 @@
         <v>1.48</v>
       </c>
       <c r="C14" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="D14" t="n">
         <v>6</v>
@@ -660,144 +660,14 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>dYUosgsB</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>U3Cs29yR</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>vcKjtDdH</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Me49cTqr</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>ImJfuXBN</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>0n3Ddmal</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>SM4QZAZp</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>URr9bfCo</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>QDIbviRT</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>rVnDcERi</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>xhnHdYtb</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>GroLehd4</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YJuQfCBA</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/usa/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/usa/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,225 +448,209 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>A3m1Vera</t>
+          <t>CAvUgWQG</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="C2" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="D2" t="n">
-        <v>4.33</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8lOY3V6E</t>
+          <t>6XwYhjtN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.88</v>
+        <v>1.67</v>
       </c>
       <c r="C3" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.45</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ITj9TZCB</t>
+          <t>rBhIe7Ef</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="C4" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lfn5UFc5</t>
+          <t>I7sxhAeT</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="C5" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dKkDSgSH</t>
+          <t>OlK4mU3p</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="C6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D6" t="n">
         <v>4.75</v>
-      </c>
-      <c r="D6" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vquIRDsO</t>
+          <t>2uJ8nlJj</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.44</v>
+        <v>2.7</v>
       </c>
       <c r="C7" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="D7" t="n">
-        <v>6.1</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jDDw3kMK</t>
+          <t>jeCjBXei</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="C8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D8" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>xUcLQXdU</t>
+          <t>CA0a9BQ3</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="D9" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EkZQoHSu</t>
+          <t>UoBfAiBc</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="D10" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>htYUpyrn</t>
+          <t>tdBLfRT0</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="C11" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="D11" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>AHSZqech</t>
+          <t>QD438VuA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="C12" t="n">
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>l8RwqFCb</t>
+          <t>zJAPgoq7</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="C13" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="D13" t="n">
-        <v>2.45</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>foKU4Bi8</t>
+          <t>Kz477keG</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.48</v>
+        <v>2.5</v>
       </c>
       <c r="C14" t="n">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>rVQsrZR4</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="C15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/usa/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/data/usa/p6_deployment/data_preparation/format_data/df_match_odds_form.xlsx
@@ -448,209 +448,209 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CAvUgWQG</t>
+          <t>YuZ4CywD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="C2" t="n">
         <v>3.6</v>
       </c>
       <c r="D2" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6XwYhjtN</t>
+          <t>UuWb8pb0</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="C3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rBhIe7Ef</t>
+          <t>llHizuVJ</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="C4" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>I7sxhAeT</t>
+          <t>CWX8BehJ</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="C5" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="D5" t="n">
-        <v>4.75</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>OlK4mU3p</t>
+          <t>pK2NUIhs</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="C6" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="D6" t="n">
-        <v>4.75</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2uJ8nlJj</t>
+          <t>MFWf9Qrf</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="C7" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.45</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jeCjBXei</t>
+          <t>r5LQTx8m</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="C8" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CA0a9BQ3</t>
+          <t>QTAVSdNg</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="C9" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="D9" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>UoBfAiBc</t>
+          <t>4K9ZRGx0</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="C10" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="D10" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>tdBLfRT0</t>
+          <t>YgEwRzh6</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="C11" t="n">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="D11" t="n">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>QD438VuA</t>
+          <t>CpDsQf7C</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>3.9</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>zJAPgoq7</t>
+          <t>SvGeZbpQ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="C13" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Kz477keG</t>
+          <t>f92nPEMI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="C14" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5</v>
+        <v>5.25</v>
       </c>
     </row>
   </sheetData>
